--- a/input_data_2040_aggregated.xlsx
+++ b/input_data_2040_aggregated.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="37">
   <si>
     <t>r</t>
   </si>
@@ -89,6 +89,12 @@
   </si>
   <si>
     <t>kappa_Q</t>
+  </si>
+  <si>
+    <t>f_hold</t>
+  </si>
+  <si>
+    <t>c_inv</t>
   </si>
   <si>
     <t>exporter</t>
@@ -541,10 +547,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -584,8 +590,14 @@
       <c r="M1" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -625,8 +637,14 @@
       <c r="M2">
         <v>0.0001</v>
       </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>35.7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -666,8 +684,14 @@
       <c r="M3">
         <v>0.0001</v>
       </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -707,8 +731,14 @@
       <c r="M4">
         <v>0.0001</v>
       </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>44.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -748,8 +778,14 @@
       <c r="M5">
         <v>0.0001</v>
       </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>37.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -788,6 +824,12 @@
       </c>
       <c r="M6">
         <v>0.0001</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>40.8</v>
       </c>
     </row>
   </sheetData>
@@ -802,7 +844,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
@@ -932,39 +974,39 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5">
         <v>0.05</v>
@@ -972,10 +1014,10 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
